--- a/测试用例.xlsx
+++ b/测试用例.xlsx
@@ -29,7 +29,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+  <si>
+    <t>keywords</t>
+  </si>
   <si>
     <t>hardware</t>
   </si>
@@ -968,8 +971,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
@@ -984,6 +987,11 @@
     <row r="3" spans="1:1">
       <c r="A3" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/测试用例.xlsx
+++ b/测试用例.xlsx
@@ -29,18 +29,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t>keywords</t>
   </si>
   <si>
+    <t>category</t>
+  </si>
+  <si>
     <t>hardware</t>
+  </si>
+  <si>
+    <t>Industry Insights</t>
   </si>
   <si>
     <t>Lighting accessories</t>
   </si>
   <si>
     <t>lamp holder</t>
+  </si>
+  <si>
+    <t>Technical Guides</t>
   </si>
 </sst>
 </file>
@@ -971,27 +980,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="21.4513274336283" customWidth="1"/>
+    <col min="2" max="2" width="17.7256637168142" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/测试用例.xlsx
+++ b/测试用例.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,55 +415,79 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>universal joint</v>
+        <v>lighting hardware manufacturer</v>
       </c>
       <c r="B2" t="str">
-        <v>Technical Guides</v>
+        <v>Technical Guides_x000d_</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>wall lamp set</v>
+        <v>lighting accessories manufacturer</v>
       </c>
       <c r="B3" t="str">
-        <v>Technical Guides</v>
+        <v>Technical Guides_x000d_</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>floor lamp set</v>
+        <v>custom lighting hardware</v>
       </c>
       <c r="B4" t="str">
-        <v>Technical Guides</v>
+        <v>Technical Guides_x000d_</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>hardware processing</v>
+        <v>lamp parts manufacturer</v>
       </c>
       <c r="B5" t="str">
-        <v>Industry Insights</v>
+        <v>Technical Guides_x000d_</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>surface treatment</v>
+        <v>OEM lighting accessories</v>
       </c>
       <c r="B6" t="str">
-        <v>Industry Insights</v>
+        <v>Technical Guides</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>surface treatment</v>
+        <v>lighting hardware supplier comparison</v>
       </c>
       <c r="B7" t="str">
-        <v>Technical Guides</v>
+        <v>Industry Insights_x000d_</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>best lighting accessories manufacturer</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Industry Insights_x000d_</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>how to compare lamp parts suppliers</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Industry Insights_x000d_</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>OEM vs ODM lighting hardware</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Industry Insights</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B10"/>
   </ignoredErrors>
 </worksheet>
 </file>
